--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N74_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N74_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>57.98695271379709</v>
+        <v>9.422879815992028</v>
       </c>
       <c r="D2" t="n">
-        <v>10.77919373548564</v>
+        <v>1.751618982016417</v>
       </c>
       <c r="E2" t="n">
-        <v>5.248509722083038</v>
+        <v>0.8528828298384936</v>
       </c>
       <c r="F2" t="n">
-        <v>19.28015316751302</v>
+        <v>3.133024889720867</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.71454433577293</v>
+        <v>7.428613454563102</v>
       </c>
       <c r="D3" t="n">
-        <v>26.92897530490908</v>
+        <v>4.375958487047726</v>
       </c>
       <c r="E3" t="n">
-        <v>5.248509722083038</v>
+        <v>0.8528828298384936</v>
       </c>
       <c r="F3" t="n">
-        <v>19.28015316751302</v>
+        <v>3.133024889720867</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>56.56282230074184</v>
+        <v>9.191458623870549</v>
       </c>
       <c r="D4" t="n">
-        <v>55.01211525797017</v>
+        <v>8.939468729420152</v>
       </c>
       <c r="E4" t="n">
-        <v>5.248509722083038</v>
+        <v>0.8528828298384936</v>
       </c>
       <c r="F4" t="n">
-        <v>19.28015316751302</v>
+        <v>3.133024889720867</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>58.59560475087077</v>
+        <v>9.5217857720165</v>
       </c>
       <c r="D5" t="n">
-        <v>56.33345023871792</v>
+        <v>9.154185663791663</v>
       </c>
       <c r="E5" t="n">
-        <v>5.248509722083038</v>
+        <v>0.8528828298384936</v>
       </c>
       <c r="F5" t="n">
-        <v>19.28015316751302</v>
+        <v>3.133024889720867</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
